--- a/product_upload/packages/53/file.xlsx
+++ b/product_upload/packages/53/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -838,6 +843,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>Cholib 145/20</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-5263035D589D</t>
         </is>
       </c>
@@ -861,7 +871,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1032,6 +1042,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>Cholib 145/40</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-D32C9998B11B</t>
         </is>
       </c>
@@ -1055,7 +1070,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1222,6 +1237,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>Regaine Foam for Men 5%</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-B11D8AB913E1</t>
         </is>
       </c>
@@ -1245,7 +1265,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1408,6 +1428,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>Fusizone-F</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-347B346D43E6</t>
         </is>
       </c>
@@ -1431,7 +1456,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1598,6 +1623,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>Uptravi 200 mcg titration pack</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-4675CDA52E3D</t>
         </is>
       </c>
@@ -1621,7 +1651,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1784,6 +1814,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Uptravi 600 mcg </t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-D4C45863183E</t>
         </is>
       </c>
@@ -1807,7 +1842,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1974,6 +2009,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>Uptravi 1000 mcg</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-778883F66E64</t>
         </is>
       </c>
@@ -1997,7 +2037,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2164,6 +2204,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Uptravi 1200 mcg </t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-28E11D983910</t>
         </is>
       </c>
@@ -2187,7 +2232,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2350,6 +2395,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>JANUVIA 25 mg</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-63B827DA5780</t>
         </is>
       </c>
@@ -2373,7 +2423,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2536,6 +2586,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>JANUVIA 50 mg</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-7C5502033B41</t>
         </is>
       </c>
@@ -2559,7 +2614,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2726,6 +2781,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>Pantrox</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-8AEFC3160A56</t>
         </is>
       </c>
@@ -2749,7 +2809,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2916,6 +2976,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>NovoRapid</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-4831AB90B3F5</t>
         </is>
       </c>
@@ -2939,7 +3004,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3100,6 +3165,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>Maxeva</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-07D2DCD0E7AD</t>
         </is>
       </c>
@@ -3123,7 +3193,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3296,6 +3366,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>Prodein Plus</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-3500202918D7</t>
         </is>
       </c>
@@ -3319,7 +3394,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3482,6 +3557,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>Rolitac XL</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-0945F1A0250D</t>
         </is>
       </c>
@@ -3505,7 +3585,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3672,6 +3752,11 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>Rolitac XL</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-C44D8F982989</t>
         </is>
       </c>
@@ -3695,7 +3780,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3866,6 +3951,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>Rolitac XL</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-73DBAE3E58F0</t>
         </is>
       </c>
@@ -3889,7 +3979,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4056,6 +4146,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>Rolitac XL</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-056C9A1FB3CF</t>
         </is>
       </c>
@@ -4079,7 +4174,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4236,6 +4331,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>Inment</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-BCDC137610D2</t>
         </is>
       </c>
@@ -4259,7 +4359,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4422,6 +4522,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Uptravi 1400 mcg </t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-9A11B4E06A1D</t>
         </is>
       </c>
@@ -4445,7 +4550,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4604,6 +4709,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>Uptravi 1600 mcg</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-E5AEAF8B6310</t>
         </is>
       </c>
@@ -4627,7 +4737,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4794,6 +4904,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>Voricet</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-A1AAD9366AC9</t>
         </is>
       </c>
@@ -4817,7 +4932,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4988,6 +5103,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>Adtralza</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-21EA784CC2A4</t>
         </is>
       </c>
@@ -5011,7 +5131,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5190,6 +5310,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>NGENLA</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-941F4203839E</t>
         </is>
       </c>
@@ -5213,7 +5338,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5392,6 +5517,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>NGENLA</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-F9A68D7076F6</t>
         </is>
       </c>
@@ -5415,7 +5545,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5584,6 +5714,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>Omnicef</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-E4750B2C2503</t>
         </is>
       </c>
@@ -5607,7 +5742,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5780,6 +5915,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>Ticagrelor SPC F.C. Tablets</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-D05DDF8B7FC5</t>
         </is>
       </c>
@@ -5803,7 +5943,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5966,6 +6106,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>Ventra</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-993742EE7245</t>
         </is>
       </c>
@@ -5989,7 +6134,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6150,6 +6295,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>Ventra</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-4C898A8F4667</t>
         </is>
       </c>
@@ -6173,7 +6323,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6336,6 +6486,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>Pantrox</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-6481E55E3B5A</t>
         </is>
       </c>
@@ -6359,7 +6514,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6532,6 +6687,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>FARINOX 20MG/0.2ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-0B6A2A1EBB87</t>
         </is>
       </c>
@@ -6555,7 +6715,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6724,6 +6884,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>FARINOX 40MG/0.4ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-8AA6CBF5CDC8</t>
         </is>
       </c>
@@ -6747,7 +6912,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6920,6 +7085,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>FARINOX 60MG/0.6ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-CD3C7D01E45B</t>
         </is>
       </c>
@@ -6943,7 +7113,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7120,6 +7290,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>FARINOX 80MG/0.8ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-F43A17C0A00F</t>
         </is>
       </c>
@@ -7143,7 +7318,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7302,6 +7477,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>Vapir</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-ABA133B7CC71</t>
         </is>
       </c>
@@ -7325,7 +7505,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7496,6 +7676,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>Scemblix</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-82CE79B46102</t>
         </is>
       </c>
@@ -7519,7 +7704,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7682,6 +7867,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>Scemblix</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-11EA627F2AA1</t>
         </is>
       </c>
@@ -7705,7 +7895,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7868,6 +8058,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>Votellaz</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-CA08EC6BC11D</t>
         </is>
       </c>
@@ -7891,7 +8086,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8054,6 +8249,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>Intuniv XR</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-CFFBF33B9AD0</t>
         </is>
       </c>
@@ -8077,7 +8277,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8240,6 +8440,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>Intuniv XR</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-D6C6BE29B446</t>
         </is>
       </c>
@@ -8263,7 +8468,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8422,6 +8627,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>Intuniv XR</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-20AF25145028</t>
         </is>
       </c>
@@ -8445,7 +8655,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8612,6 +8822,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>Intuniv XR</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-32DCD124C300</t>
         </is>
       </c>
@@ -8635,7 +8850,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8806,6 +9021,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>Sicfrex</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-C18174300339</t>
         </is>
       </c>
@@ -8829,7 +9049,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8996,6 +9216,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>Bivocard</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-25570AEEF178</t>
         </is>
       </c>
@@ -9019,7 +9244,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9182,6 +9407,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>Klavox ES-600</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-CE50744BC69B</t>
         </is>
       </c>
@@ -9205,7 +9435,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9368,6 +9598,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>Aprolin</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-713E2D062484</t>
         </is>
       </c>
@@ -9391,7 +9626,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9554,6 +9789,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>ARNALTEM</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-0A5ABA870F2D</t>
         </is>
       </c>
@@ -9577,7 +9817,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9740,6 +9980,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>Macimit</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-9C0B9A529BD1</t>
         </is>
       </c>
@@ -9763,7 +10008,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9918,6 +10163,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>Amlovan</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-A5E2EDEBD65F</t>
         </is>
       </c>
@@ -9941,7 +10191,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10100,6 +10350,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>Imla</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-A5B449AAF8B2</t>
         </is>
       </c>
@@ -10123,7 +10378,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10290,6 +10545,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>Sogroya 5 mg / 1.5ml</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-BCB663B435DD</t>
         </is>
       </c>
@@ -10313,7 +10573,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10480,6 +10740,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>Flopadex</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-7CFB2BBFFB80</t>
         </is>
       </c>
@@ -10503,7 +10768,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10674,6 +10939,11 @@
       </c>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>Sicfrex</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-9656110107E7</t>
         </is>
       </c>
@@ -10697,7 +10967,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10864,6 +11134,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>Sicfrex</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-185B6D33C3A4</t>
         </is>
       </c>
@@ -10887,7 +11162,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11042,6 +11317,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>Amlovan</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-3C8FBB4F5350</t>
         </is>
       </c>
@@ -11065,7 +11345,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11224,6 +11504,11 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>Bosentan OHRE Pharma</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-61A10505A859</t>
         </is>
       </c>
@@ -11247,7 +11532,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11426,6 +11711,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>Nurtec</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-A37D79494ABE</t>
         </is>
       </c>
@@ -11449,7 +11739,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11620,6 +11910,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>Flexall Ultra</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-1500BE6901F1</t>
         </is>
       </c>
@@ -11643,7 +11938,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11806,6 +12101,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>Imodium Plus Caplets</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-E071AD4ED553</t>
         </is>
       </c>
@@ -11829,7 +12129,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11996,6 +12296,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>BioVitin</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-429365DF7808</t>
         </is>
       </c>
@@ -12019,7 +12324,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12178,6 +12483,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>AJOVY</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-442CE5F02BF4</t>
         </is>
       </c>
@@ -12201,7 +12511,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12356,6 +12666,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>Coxido</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-AEF7174166F5</t>
         </is>
       </c>
@@ -12379,7 +12694,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12540,6 +12855,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>Vertella</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-EE66D6163E20</t>
         </is>
       </c>
@@ -12563,7 +12883,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12718,6 +13038,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>Vardenafil Eva</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-0C6B673A6FF8</t>
         </is>
       </c>
@@ -12741,7 +13066,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12904,6 +13229,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>ClariSpray Original</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-12F17745CD4D</t>
         </is>
       </c>
@@ -12927,7 +13257,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13086,6 +13416,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>ClariSpray Menthol</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-256A8AF0A6BA</t>
         </is>
       </c>
@@ -13109,7 +13444,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13268,6 +13603,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>Sensityn</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-D3219963256E</t>
         </is>
       </c>
@@ -13291,7 +13631,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13458,6 +13798,11 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>Sensityn</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-D604F8226A49</t>
         </is>
       </c>
@@ -13481,7 +13826,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13640,6 +13985,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>Kolitarda</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-7BE45D27A989</t>
         </is>
       </c>
@@ -13663,7 +14013,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13822,6 +14172,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>Kolitarda</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-12428926B21C</t>
         </is>
       </c>
@@ -13845,7 +14200,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14004,6 +14359,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Evrenzo </t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-66563BDA721C</t>
         </is>
       </c>
@@ -14027,7 +14387,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14194,6 +14554,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>ARNALTEM</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-D48432DFA1FB</t>
         </is>
       </c>
@@ -14217,7 +14582,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14384,6 +14749,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>ARNALTEM</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-B616F4B3C7ED</t>
         </is>
       </c>
@@ -14407,7 +14777,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14572,6 +14942,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>Fumadi</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-110DE2783F80</t>
         </is>
       </c>
@@ -14595,7 +14970,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14764,6 +15139,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>Fumadi</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-CFF19E4CCCF0</t>
         </is>
       </c>
@@ -14787,7 +15167,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14946,6 +15326,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>Levar</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-C4CCE1DBFC76</t>
         </is>
       </c>
@@ -14969,7 +15354,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15128,6 +15513,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>Levar</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-BFBB1AD29696</t>
         </is>
       </c>
@@ -15151,7 +15541,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15316,6 +15706,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>Glycelax</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-20883F1D8A88</t>
         </is>
       </c>
@@ -15339,7 +15734,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15502,6 +15897,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tezspire 210 mg per 1.9 ml Pre-filled syringe	</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-94D7E4AFA2E4</t>
         </is>
       </c>
@@ -15525,7 +15925,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15698,6 +16098,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>Prograf</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-B7CACF97E160</t>
         </is>
       </c>
@@ -15721,7 +16126,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15888,6 +16293,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>Dezeroga</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-3A7B0C496CC6</t>
         </is>
       </c>
@@ -15911,7 +16321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16080,6 +16490,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>Pratima Trio</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-9F5F99B12E09</t>
         </is>
       </c>
@@ -16103,7 +16518,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16272,6 +16687,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>Pratima Trio</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-B58A3B3C475F</t>
         </is>
       </c>
@@ -16295,7 +16715,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16464,6 +16884,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>Pratima Trio</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-6E6B6150A433</t>
         </is>
       </c>
@@ -16487,7 +16912,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16656,6 +17081,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>Pratima Trio</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-B6282E29B723</t>
         </is>
       </c>
@@ -16679,7 +17109,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16842,6 +17272,11 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>Quenfil</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-1958A52A01A1</t>
         </is>
       </c>
@@ -16865,7 +17300,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17026,6 +17461,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>Mixif</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-BD51B0940ADE</t>
         </is>
       </c>
@@ -17049,7 +17489,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17210,6 +17650,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>Lusam</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-85C191A4F2E3</t>
         </is>
       </c>
@@ -17233,7 +17678,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17386,6 +17831,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>Lusam</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-062028252594</t>
         </is>
       </c>
@@ -17409,7 +17859,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17566,6 +18016,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>Lusam</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-8A6A338D8B8F</t>
         </is>
       </c>
@@ -17589,7 +18044,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17746,6 +18201,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>Lusam</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-A80E7175F2A0</t>
         </is>
       </c>
@@ -17769,7 +18229,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17930,6 +18390,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>Lusam</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-1378829D8491</t>
         </is>
       </c>
@@ -17953,7 +18418,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18126,6 +18591,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>Glycelax</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-37BE8D169480</t>
         </is>
       </c>
@@ -18149,7 +18619,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18308,6 +18778,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>JNESTY</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-81964B1C6DC0</t>
         </is>
       </c>
@@ -18331,7 +18806,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18498,6 +18973,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Coguperin 20 mg per  0.2 ml </t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-0E79FCA8FB0D</t>
         </is>
       </c>
@@ -18521,7 +19001,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18680,6 +19160,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>Coguperin 40 mg per 0.4 ml</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-A92F39AF2CB9</t>
         </is>
       </c>
@@ -18703,7 +19188,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18870,6 +19355,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>Coguperin 60 mg per 0.6 ml</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-8BBD95E017B0</t>
         </is>
       </c>
@@ -18893,7 +19383,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19056,6 +19546,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Coguperin 80 mg per 0.8 ml </t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-B9A75C2EE36F</t>
         </is>
       </c>
@@ -19079,7 +19574,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19240,6 +19735,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>Effyren</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-F9728A3E976A</t>
         </is>
       </c>
@@ -19263,7 +19763,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19425,6 +19925,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Amlohope Plus</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-AEA532D9062A</t>
         </is>
@@ -19441,7 +19946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19487,100 +19992,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19612,7 +20122,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19627,92 +20137,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-36148</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>68.12</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>519</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19744,7 +20259,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19759,92 +20274,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-20260</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>42.32</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>520</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19876,7 +20396,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19891,92 +20411,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-61258</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>480.27</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>521</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20008,7 +20533,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20023,92 +20548,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-84099</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>483.08</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>522</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20140,7 +20670,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20155,92 +20685,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-48859</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>470.94</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>523</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20272,7 +20807,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20287,92 +20822,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-44262</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>306.1</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>524</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20404,7 +20944,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20419,92 +20959,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-22387</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>202.25</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>525</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20536,7 +21081,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20551,92 +21096,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-24050</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>105.03</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>526</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20668,7 +21218,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20683,92 +21233,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-76058</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>120.42</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>527</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20800,7 +21355,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20815,92 +21370,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-22762</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>231.63</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>528</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20932,7 +21492,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20947,92 +21507,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-13649</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>224.68</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>529</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21049,7 +21614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21155,6 +21720,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21190,7 +21765,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21255,6 +21830,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-AF8CADA8BDED</t>
         </is>
@@ -21291,7 +21876,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21356,6 +21941,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-A1B8A422C2EE</t>
         </is>
@@ -21392,7 +21987,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21457,6 +22052,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-F195C30B5548</t>
         </is>
@@ -21493,7 +22098,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21558,6 +22163,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-682E4FFDF813</t>
         </is>
@@ -21594,7 +22209,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21659,6 +22274,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-77C240F7C3E5</t>
         </is>
@@ -21695,7 +22320,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21760,6 +22385,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-CEA3CB6EC0D9</t>
         </is>
@@ -21796,7 +22431,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21861,6 +22496,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-AFCD711A7841</t>
         </is>
@@ -21897,7 +22542,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21962,6 +22607,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-76F0F0E6689D</t>
         </is>
@@ -21998,7 +22653,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22063,6 +22718,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-7D48E16C75FF</t>
         </is>
@@ -22099,7 +22764,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22164,6 +22829,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-852311DC28EE</t>
         </is>
@@ -22200,7 +22875,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22265,6 +22940,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-1AAFF23BC5E1</t>
         </is>
@@ -22301,7 +22986,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22366,6 +23051,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-767857B40035</t>
         </is>
@@ -22402,7 +23097,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22467,6 +23162,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-EFAF3FCBBBC0</t>
         </is>
@@ -22503,7 +23208,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22568,6 +23273,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-EA99F3BD0C8F</t>
         </is>
@@ -22604,7 +23319,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22669,6 +23384,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-6003B289377C</t>
         </is>
@@ -22705,7 +23430,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22770,6 +23495,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-E1E44D00C907</t>
         </is>
@@ -22806,7 +23541,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22871,6 +23606,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-268908167F1D</t>
         </is>
@@ -22907,7 +23652,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22972,6 +23717,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-60F570E398A1</t>
         </is>
@@ -23008,7 +23763,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23073,6 +23828,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-8159022AF67F</t>
         </is>
@@ -23109,7 +23874,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23174,6 +23939,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-E56FCC4C9673</t>
         </is>

--- a/product_upload/packages/53/file.xlsx
+++ b/product_upload/packages/53/file.xlsx
@@ -1078,8 +1078,16 @@
           <t>9716903332-464-231189230622</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Regaine Foam for Men 5%</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Regaine Foam for Men 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1273,8 +1281,16 @@
           <t>0367912979-250-475826705043</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Fusizone-F</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fusizone-F detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1464,8 +1480,16 @@
           <t>0787313522-310-619367954784</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Uptravi 200 mcg titration pack</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Uptravi 200 mcg titration pack detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1659,8 +1683,16 @@
           <t>4216557873-019-994100437407</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Uptravi 600 mcg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Uptravi 600 mcg detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1850,8 +1882,16 @@
           <t>2400416712-321-671212722300</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Uptravi 1000 mcg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Uptravi 1000 mcg detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2045,8 +2085,16 @@
           <t>7138365344-379-583156926438</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Uptravi 1200 mcg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Uptravi 1200 mcg detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2240,8 +2288,16 @@
           <t>5326216278-479-165568893859</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JANUVIA 25 mg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>JANUVIA 25 mg detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2431,8 +2487,16 @@
           <t>0287546494-310-683898113100</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JANUVIA 50 mg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>JANUVIA 50 mg detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2622,8 +2686,16 @@
           <t>1977917528-115-943899653891</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pantrox</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pantrox detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2817,8 +2889,16 @@
           <t>1096854840-719-606279267855</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NovoRapid</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NovoRapid detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3012,8 +3092,16 @@
           <t>3368127434-939-801551246529</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Maxeva</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Maxeva detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3402,8 +3490,16 @@
           <t>3420678809-734-430209693138</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rolitac XL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Rolitac XL detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3593,8 +3689,16 @@
           <t>8324669193-654-989350928487</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rolitac XL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Rolitac XL detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3987,8 +4091,16 @@
           <t>4059264816-258-079328590294</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rolitac XL</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Rolitac XL detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4182,8 +4294,16 @@
           <t>0567091855-147-717041655542</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Inment</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Inment detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4367,8 +4487,16 @@
           <t>2323036083-858-077359897291</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Uptravi 1400 mcg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Uptravi 1400 mcg detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4558,8 +4686,16 @@
           <t>4393025777-732-925264262834</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Uptravi 1600 mcg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Uptravi 1600 mcg detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4745,8 +4881,16 @@
           <t>5156747649-498-920561642946</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Voricet</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Voricet detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -5951,8 +6095,16 @@
           <t>4535971743-433-742177550448</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ventra</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Ventra detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -6142,8 +6294,16 @@
           <t>8385865562-902-280123366141</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ventra</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ventra detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6331,8 +6491,16 @@
           <t>1199852512-073-910995648262</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pantrox</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Pantrox detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -7326,8 +7494,16 @@
           <t>4574645558-918-887789984689</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vapir</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Vapir detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7712,8 +7888,16 @@
           <t>3001200034-760-151624565755</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Scemblix</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Scemblix detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7903,8 +8087,16 @@
           <t>5461368214-783-936556720102</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Votellaz</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Votellaz detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -8094,8 +8286,16 @@
           <t>1643301062-971-592707791479</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Intuniv XR</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Intuniv XR detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8285,8 +8485,16 @@
           <t>7197927389-974-191744397151</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Intuniv XR</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Intuniv XR detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8476,8 +8684,16 @@
           <t>6445681592-216-514846892027</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Intuniv XR</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Intuniv XR detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8663,8 +8879,16 @@
           <t>8735098302-909-733968557900</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Intuniv XR</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Intuniv XR detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -10016,8 +10240,16 @@
           <t>6542669480-747-852399439817</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Amlovan</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Amlovan detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10199,8 +10431,16 @@
           <t>3232119185-032-771245410541</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Imla</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Imla detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10386,8 +10626,16 @@
           <t>4207423112-050-903100233794</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sogroya 5 mg / 1.5ml</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sogroya 5 mg / 1.5ml detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -11170,8 +11418,16 @@
           <t>0684798208-819-090147107559</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Amlovan</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Amlovan detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11353,8 +11609,16 @@
           <t>3234733101-801-852577801763</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Bosentan OHRE Pharma</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bosentan OHRE Pharma detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11946,8 +12210,16 @@
           <t>4619693708-704-098797867874</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Imodium Plus Caplets</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Imodium Plus Caplets detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12332,8 +12604,16 @@
           <t>8215746938-633-812942561636</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AJOVY</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>AJOVY detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12519,8 +12799,16 @@
           <t>6557076790-238-123544749425</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Coxido</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Coxido detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12702,8 +12990,16 @@
           <t>4637587870-189-958666248665</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vertella</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Vertella detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>Pharma Pharmaceutical Industries (PPI)</t>
@@ -12891,8 +13187,16 @@
           <t>4238082880-520-592122667392</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vardenafil Eva</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Vardenafil Eva detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13074,8 +13378,16 @@
           <t>6810058437-241-179309408692</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ClariSpray Original</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ClariSpray Original detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13265,8 +13577,16 @@
           <t>0215199392-551-016166443054</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ClariSpray Menthol</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ClariSpray Menthol detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13834,8 +14154,16 @@
           <t>8509271151-995-872872045283</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Kolitarda</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kolitarda detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14021,8 +14349,16 @@
           <t>2138931269-980-619168259875</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Kolitarda</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kolitarda detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14208,8 +14544,16 @@
           <t>0433537710-328-030725147260</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Evrenzo</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Evrenzo detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14785,8 +15129,16 @@
           <t>2872299363-529-885362035624</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Fumadi</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Fumadi detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>Dallah Pharma Factory</t>
@@ -14978,8 +15330,16 @@
           <t>6642860507-735-613079268621</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Fumadi</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Fumadi detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
           <t>Dallah Pharma Factory</t>
@@ -15175,8 +15535,16 @@
           <t>6591328475-872-213054080321</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Levar</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Levar detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15362,8 +15730,16 @@
           <t>2161427181-152-855695998850</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Levar</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Levar detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15742,8 +16118,16 @@
           <t>2542615092-571-829208748351</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tezspire 210 mg per 1.9 ml Pre-filled syringe</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Tezspire 210 mg per 1.9 ml Pre-filled syringe detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -16134,8 +16518,16 @@
           <t>7270595398-738-986650032296</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dezeroga</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Dezeroga detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -17117,8 +17509,16 @@
           <t>0632657627-700-323179350727</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Quenfil</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Quenfil detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17308,8 +17708,16 @@
           <t>6161782671-901-897381204934</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Mixif</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Mixif detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17497,8 +17905,16 @@
           <t>3250910627-713-828133977797</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lusam</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Lusam detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17686,8 +18102,16 @@
           <t>3934244409-130-654129007734</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lusam</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Lusam detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17867,8 +18291,16 @@
           <t>8875144850-870-333309778504</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lusam</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Lusam detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18052,8 +18484,16 @@
           <t>5261052650-532-250013919508</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lusam</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Lusam detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18237,8 +18677,16 @@
           <t>0398990152-649-099945120118</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lusam</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Lusam detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18627,8 +19075,16 @@
           <t>6079226743-834-225812492706</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JNESTY</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>JNESTY detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18814,8 +19270,16 @@
           <t>1496687103-611-656225538493</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Coguperin 20 mg per  0.2 ml</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Coguperin 20 mg per  0.2 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -19009,8 +19473,16 @@
           <t>3097460663-163-838758601081</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Coguperin 40 mg per 0.4 ml</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Coguperin 40 mg per 0.4 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -19196,8 +19668,16 @@
           <t>5409996244-985-166702495833</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Coguperin 60 mg per 0.6 ml</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Coguperin 60 mg per 0.6 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -19391,8 +19871,16 @@
           <t>9800832719-541-798017349286</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Coguperin 80 mg per 0.8 ml</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Coguperin 80 mg per 0.8 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19582,8 +20070,16 @@
           <t>8843074877-465-305736978303</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Effyren</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Effyren detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19771,8 +20267,16 @@
           <t>8521249226-035-372976054757</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Amlohope Plus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Amlohope Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/53/file.xlsx
+++ b/product_upload/packages/53/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22118,7 +22118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22199,40 +22199,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22312,38 +22317,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>341.6</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-AF8CADA8BDED</t>
         </is>
@@ -22423,38 +22433,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>432.48</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-A1B8A422C2EE</t>
         </is>
@@ -22534,38 +22549,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>142.29</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-F195C30B5548</t>
         </is>
@@ -22645,38 +22665,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>269.79</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-682E4FFDF813</t>
         </is>
@@ -22756,38 +22781,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>115.29</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-77C240F7C3E5</t>
         </is>
@@ -22867,38 +22897,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>127.76</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-CEA3CB6EC0D9</t>
         </is>
@@ -22978,38 +23013,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>142.43</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-AFCD711A7841</t>
         </is>
@@ -23089,38 +23129,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>480.01</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-76F0F0E6689D</t>
         </is>
@@ -23200,38 +23245,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>452.06</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-7D48E16C75FF</t>
         </is>
@@ -23311,38 +23361,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>190.31</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-852311DC28EE</t>
         </is>
@@ -23422,38 +23477,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>59.99</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-1AAFF23BC5E1</t>
         </is>
@@ -23533,38 +23593,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>407.79</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-767857B40035</t>
         </is>
@@ -23644,38 +23709,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>425.92</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-EFAF3FCBBBC0</t>
         </is>
@@ -23755,38 +23825,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>250.39</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-EA99F3BD0C8F</t>
         </is>
@@ -23866,38 +23941,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>105.23</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-6003B289377C</t>
         </is>
@@ -23977,38 +24057,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>386.63</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-E1E44D00C907</t>
         </is>
@@ -24088,38 +24173,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>210.71</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-268908167F1D</t>
         </is>
@@ -24199,38 +24289,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>412.36</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-60F570E398A1</t>
         </is>
@@ -24310,38 +24405,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>393.19</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-8159022AF67F</t>
         </is>
@@ -24421,38 +24521,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>126.02</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-E56FCC4C9673</t>
         </is>
